--- a/target/generatedData.xlsx
+++ b/target/generatedData.xlsx
@@ -6,40 +6,15 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hospitals" r:id="rId3" sheetId="1"/>
-    <sheet name="Top Cities" r:id="rId4" sheetId="2"/>
+    <sheet name="Top Cities" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
-  <si>
-    <t>Hospital Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>City Name</t>
-  </si>
-  <si>
-    <t>Manipal Hospital Varthur Road (formerly Columbia Asia Hospital)</t>
-  </si>
-  <si>
-    <t>Manipal Hospitals</t>
-  </si>
-  <si>
-    <t>Koshys Hospital</t>
-  </si>
-  <si>
-    <t>Motherhood Hospital</t>
-  </si>
-  <si>
-    <t>Sagar Hospitals</t>
-  </si>
-  <si>
-    <t>Apollo Cradle &amp; Children’s Hospital</t>
-  </si>
-  <si>
-    <t>Cloudnine Hospital - Old Airport Road</t>
   </si>
   <si>
     <t>Bangalore</t>
@@ -118,22 +93,22 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -159,59 +134,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>